--- a/research/traditional_assets/database/data/jordan/jordan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3655</v>
+        <v>-0.101</v>
       </c>
       <c r="E2">
-        <v>-0.262</v>
+        <v>-0.327</v>
       </c>
       <c r="G2">
-        <v>-0.6659574468085105</v>
+        <v>0.1823361823361823</v>
       </c>
       <c r="H2">
-        <v>-0.6659574468085105</v>
+        <v>0.1823361823361823</v>
       </c>
       <c r="I2">
-        <v>-0.9</v>
+        <v>-0.09116809116809117</v>
       </c>
       <c r="J2">
-        <v>-0.7628571428571429</v>
+        <v>-0.08205128205128205</v>
       </c>
       <c r="K2">
-        <v>-0.39</v>
+        <v>-0.013</v>
       </c>
       <c r="L2">
-        <v>-0.8297872340425532</v>
+        <v>-0.009259259259259262</v>
       </c>
       <c r="M2">
-        <v>0.141</v>
+        <v>1.191</v>
       </c>
       <c r="N2">
-        <v>0.01124401913875598</v>
+        <v>0.03114539748953975</v>
       </c>
       <c r="O2">
-        <v>-0.3615384615384615</v>
+        <v>-91.6153846153846</v>
       </c>
       <c r="P2">
-        <v>0.141</v>
+        <v>1.191</v>
       </c>
       <c r="Q2">
-        <v>0.01124401913875598</v>
+        <v>0.03114539748953975</v>
       </c>
       <c r="R2">
-        <v>-0.3615384615384615</v>
+        <v>-91.6153846153846</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.44</v>
+        <v>1.869</v>
       </c>
       <c r="V2">
-        <v>0.2743221690590111</v>
+        <v>0.0488755230125523</v>
       </c>
       <c r="W2">
-        <v>-0.02064220183486238</v>
+        <v>-0.01200923787528868</v>
       </c>
       <c r="X2">
-        <v>0.07589653696689169</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="Y2">
-        <v>-0.09653873880175408</v>
+        <v>-0.1286746086272745</v>
       </c>
       <c r="Z2">
-        <v>0.02875321179493454</v>
+        <v>0.06434463794683776</v>
       </c>
       <c r="AA2">
-        <v>-0.02064220183486238</v>
+        <v>-0.01200923787528868</v>
       </c>
       <c r="AB2">
-        <v>0.07589653696689169</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="AC2">
-        <v>-0.09653873880175408</v>
+        <v>-0.1286746086272745</v>
       </c>
       <c r="AD2">
-        <v>0.181</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.181</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-3.258999999999999</v>
+        <v>-1.869</v>
       </c>
       <c r="AH2">
-        <v>0.01422844116028614</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.009933593106854727</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.351147505656718</v>
+        <v>-0.05138709411344203</v>
       </c>
       <c r="AK2">
-        <v>-0.2204857587443339</v>
+        <v>-0.08704764566159005</v>
       </c>
       <c r="AL2">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="AM2">
-        <v>0.016</v>
+        <v>-0.055</v>
       </c>
       <c r="AN2">
-        <v>-2.129411764705882</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-26.4375</v>
+        <v>-42.66666666666666</v>
       </c>
       <c r="AP2">
-        <v>38.34117647058822</v>
+        <v>-7.7551867219917</v>
       </c>
       <c r="AQ2">
-        <v>-26.4375</v>
+        <v>2.327272727272727</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Babelon Investments Company (P.L.C) (ASE:SALM)</t>
+          <t>Premier Business and Projects Co. (ASE:ACDT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.109</v>
+        <v>-0.241</v>
       </c>
       <c r="E3">
-        <v>-0.262</v>
+        <v>-0.363</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.5590551181102361</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.5590551181102361</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.4586614173228347</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.4586614173228347</v>
       </c>
       <c r="K3">
-        <v>0.018</v>
+        <v>0.251</v>
       </c>
       <c r="L3">
-        <v>0.2535211267605634</v>
+        <v>0.4940944881889764</v>
       </c>
       <c r="M3">
-        <v>0.141</v>
+        <v>0.258</v>
       </c>
       <c r="N3">
-        <v>0.04196428571428571</v>
+        <v>0.10078125</v>
       </c>
       <c r="O3">
-        <v>7.833333333333333</v>
+        <v>1.027888446215139</v>
       </c>
       <c r="P3">
-        <v>0.141</v>
+        <v>0.258</v>
       </c>
       <c r="Q3">
-        <v>0.04196428571428571</v>
+        <v>0.10078125</v>
       </c>
       <c r="R3">
-        <v>7.833333333333333</v>
+        <v>1.027888446215139</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.39</v>
+        <v>0.032</v>
       </c>
       <c r="V3">
-        <v>0.4136904761904762</v>
+        <v>0.0125</v>
       </c>
       <c r="W3">
-        <v>0.006293706293706293</v>
+        <v>0.05961995249406176</v>
       </c>
       <c r="X3">
-        <v>0.07589653696689169</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="Y3">
-        <v>-0.0696028306731854</v>
+        <v>-0.05704541825792401</v>
       </c>
       <c r="Z3">
-        <v>0.05966386554621848</v>
+        <v>0.1207798383262007</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.05539705183071802</v>
       </c>
       <c r="AB3">
-        <v>0.07589653696689169</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="AC3">
-        <v>-0.07589653696689169</v>
+        <v>-0.06126831892126775</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.39</v>
+        <v>-0.032</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,16 +815,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.7055837563451777</v>
+        <v>-0.01265822784810127</v>
       </c>
       <c r="AK3">
-        <v>-0.9586206896551723</v>
+        <v>-0.007751937984496124</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>-0.1155234657039711</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tuhama Investments Company (ASE:THMA)</t>
+          <t>Babelon Investments Company (P.L.C) (ASE:SALM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,71 +849,80 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.101</v>
+      </c>
+      <c r="E4">
+        <v>-0.291</v>
+      </c>
       <c r="G4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1.40625</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1.40625</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>-0.09</v>
+        <v>0.014</v>
       </c>
       <c r="L4">
-        <v>1.40625</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.141</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.01775818639798488</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>10.07142857142857</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.141</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.01775818639798488</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>10.07142857142857</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.1788413098236776</v>
       </c>
       <c r="W4">
-        <v>-0.02064220183486238</v>
+        <v>0.004895104895104896</v>
       </c>
       <c r="X4">
-        <v>0.07589653696689169</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="Y4">
-        <v>-0.09653873880175408</v>
+        <v>-0.1117702658568809</v>
       </c>
       <c r="Z4">
-        <v>-0.01467889908256881</v>
+        <v>0.05714285714285715</v>
       </c>
       <c r="AA4">
-        <v>-0.02064220183486238</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07589653696689169</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="AC4">
-        <v>-0.09653873880175408</v>
+        <v>-0.1166653707519858</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -919,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-1.42</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -928,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-0.2177914110429447</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>-0.9281045751633985</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ammoun International Multilateral Investments Co. (ASE:AMON)</t>
+          <t>Tuhama Investments Company (ASE:THMA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -956,26 +971,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.84</v>
-      </c>
-      <c r="G5">
-        <v>-0.6760259179265659</v>
-      </c>
-      <c r="H5">
-        <v>-0.6760259179265659</v>
-      </c>
-      <c r="I5">
-        <v>-0.7192224622030238</v>
-      </c>
-      <c r="J5">
-        <v>-0.7192224622030238</v>
-      </c>
       <c r="K5">
-        <v>-0.318</v>
-      </c>
-      <c r="L5">
-        <v>-0.6868250539956803</v>
+        <v>-0.052</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -999,73 +996,296 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.297532656023222</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>-0.02814159292035398</v>
+        <v>-0.01200923787528868</v>
       </c>
       <c r="X5">
-        <v>0.07717423487005656</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="Y5">
-        <v>-0.1053158277904105</v>
+        <v>-0.1286746086272745</v>
       </c>
       <c r="Z5">
-        <v>0.04288625416821044</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.03084475731752501</v>
+        <v>-0.01200923787528868</v>
       </c>
       <c r="AB5">
-        <v>0.07646123642019391</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="AC5">
-        <v>-0.1073059937377189</v>
+        <v>-0.1286746086272745</v>
       </c>
       <c r="AD5">
-        <v>0.181</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.181</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-1.869</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0.02559751096026022</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.01633426586048191</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.3722366062537343</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>-0.2069538257114383</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.016</v>
-      </c>
-      <c r="AN5">
-        <v>-2.129411764705882</v>
-      </c>
-      <c r="AO5">
-        <v>-20.8125</v>
-      </c>
-      <c r="AP5">
-        <v>21.98823529411764</v>
-      </c>
-      <c r="AQ5">
-        <v>-20.8125</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jordanian for Developing and Financial Investment Company (ASE:JDFI)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>-0.031</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>-0.01435185185185185</v>
+      </c>
+      <c r="X6">
+        <v>0.1166653707519858</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1310172226038376</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>-0.01435185185185185</v>
+      </c>
+      <c r="AB6">
+        <v>0.1166653707519858</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1310172226038376</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>-0</v>
+      </c>
+      <c r="AP6">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ammoun International Multilateral Investments Co. (ASE:AMON)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>1.548</v>
+      </c>
+      <c r="G7">
+        <v>-0.01207729468599034</v>
+      </c>
+      <c r="H7">
+        <v>-0.01207729468599034</v>
+      </c>
+      <c r="I7">
+        <v>-0.3357487922705314</v>
+      </c>
+      <c r="J7">
+        <v>-0.3357487922705314</v>
+      </c>
+      <c r="K7">
+        <v>-0.195</v>
+      </c>
+      <c r="L7">
+        <v>-0.2355072463768116</v>
+      </c>
+      <c r="M7">
+        <v>0.792</v>
+      </c>
+      <c r="N7">
+        <v>0.1166421207658321</v>
+      </c>
+      <c r="O7">
+        <v>-4.061538461538461</v>
+      </c>
+      <c r="P7">
+        <v>0.792</v>
+      </c>
+      <c r="Q7">
+        <v>0.1166421207658321</v>
+      </c>
+      <c r="R7">
+        <v>-4.061538461538461</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0.417</v>
+      </c>
+      <c r="V7">
+        <v>0.06141384388807069</v>
+      </c>
+      <c r="W7">
+        <v>-0.01772727272727273</v>
+      </c>
+      <c r="X7">
+        <v>0.1166653707519858</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1343926434792585</v>
+      </c>
+      <c r="Z7">
+        <v>0.08335011073082343</v>
+      </c>
+      <c r="AA7">
+        <v>-0.02798469901348903</v>
+      </c>
+      <c r="AB7">
+        <v>0.1166653707519858</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1446500697654748</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>-0.417</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.06543229248391652</v>
+      </c>
+      <c r="AK7">
+        <v>-0.04415969501217833</v>
+      </c>
+      <c r="AL7">
+        <v>0.003</v>
+      </c>
+      <c r="AM7">
+        <v>-0.055</v>
+      </c>
+      <c r="AN7">
+        <v>-0</v>
+      </c>
+      <c r="AO7">
+        <v>-92.66666666666667</v>
+      </c>
+      <c r="AP7">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="AQ7">
+        <v>5.054545454545455</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.101</v>
+        <v>1.1816</v>
       </c>
       <c r="E2">
-        <v>-0.327</v>
+        <v>0.257</v>
       </c>
       <c r="G2">
-        <v>0.1823361823361823</v>
+        <v>0.3342198581560284</v>
       </c>
       <c r="H2">
-        <v>0.1823361823361823</v>
+        <v>0.3342198581560284</v>
       </c>
       <c r="I2">
-        <v>-0.09116809116809117</v>
+        <v>0.08687943262411349</v>
       </c>
       <c r="J2">
-        <v>-0.08205128205128205</v>
+        <v>0.08175380238080296</v>
       </c>
       <c r="K2">
-        <v>-0.013</v>
+        <v>0.308</v>
       </c>
       <c r="L2">
-        <v>-0.009259259259259262</v>
+        <v>0.2730496453900709</v>
       </c>
       <c r="M2">
-        <v>1.191</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="N2">
-        <v>0.03114539748953975</v>
+        <v>0.05464098073555167</v>
       </c>
       <c r="O2">
-        <v>-91.6153846153846</v>
+        <v>3.038961038961039</v>
       </c>
       <c r="P2">
-        <v>1.191</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.03114539748953975</v>
+        <v>0.05464098073555167</v>
       </c>
       <c r="R2">
-        <v>-91.6153846153846</v>
+        <v>3.038961038961039</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.869</v>
+        <v>1.309</v>
       </c>
       <c r="V2">
-        <v>0.0488755230125523</v>
+        <v>0.07641564506713368</v>
       </c>
       <c r="W2">
-        <v>-0.01200923787528868</v>
+        <v>0.02119266055045872</v>
       </c>
       <c r="X2">
-        <v>0.1166653707519858</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="Y2">
-        <v>-0.1286746086272745</v>
+        <v>-0.07476069202447427</v>
       </c>
       <c r="Z2">
-        <v>0.06434463794683776</v>
+        <v>0.07599029911075181</v>
       </c>
       <c r="AA2">
-        <v>-0.01200923787528868</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1166653707519858</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="AC2">
-        <v>-0.1286746086272745</v>
+        <v>-0.09595335257493298</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.869</v>
+        <v>-1.309</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,28 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.05138709411344203</v>
+        <v>-0.08273813286138676</v>
       </c>
       <c r="AK2">
-        <v>-0.08704764566159005</v>
+        <v>-0.07986089927399183</v>
       </c>
       <c r="AL2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.055</v>
+        <v>-0.034</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
-      <c r="AO2">
-        <v>-42.66666666666666</v>
-      </c>
       <c r="AP2">
-        <v>-7.7551867219917</v>
+        <v>-3.490666666666666</v>
       </c>
       <c r="AQ2">
-        <v>2.327272727272727</v>
+        <v>-2.882352941176471</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier Business and Projects Co. (ASE:ACDT)</t>
+          <t>Amoun International for Investments Company (ASE:AMON)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.241</v>
-      </c>
-      <c r="E3">
-        <v>-0.363</v>
+        <v>2.321</v>
       </c>
       <c r="G3">
-        <v>0.5590551181102361</v>
+        <v>0.3910788381742739</v>
       </c>
       <c r="H3">
-        <v>0.5590551181102361</v>
+        <v>0.3910788381742739</v>
       </c>
       <c r="I3">
-        <v>0.4586614173228347</v>
+        <v>0.1182572614107884</v>
       </c>
       <c r="J3">
-        <v>0.4586614173228347</v>
+        <v>0.1182572614107884</v>
       </c>
       <c r="K3">
-        <v>0.251</v>
+        <v>0.231</v>
       </c>
       <c r="L3">
-        <v>0.4940944881889764</v>
+        <v>0.2396265560165975</v>
       </c>
       <c r="M3">
-        <v>0.258</v>
+        <v>0.795</v>
       </c>
       <c r="N3">
-        <v>0.10078125</v>
+        <v>0.1342905405405405</v>
       </c>
       <c r="O3">
-        <v>1.027888446215139</v>
+        <v>3.441558441558441</v>
       </c>
       <c r="P3">
-        <v>0.258</v>
+        <v>0.795</v>
       </c>
       <c r="Q3">
-        <v>0.10078125</v>
+        <v>0.1342905405405405</v>
       </c>
       <c r="R3">
-        <v>1.027888446215139</v>
+        <v>3.441558441558441</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.032</v>
+        <v>0.299</v>
       </c>
       <c r="V3">
-        <v>0.0125</v>
+        <v>0.05050675675675675</v>
       </c>
       <c r="W3">
-        <v>0.05961995249406176</v>
+        <v>0.02119266055045872</v>
       </c>
       <c r="X3">
-        <v>0.1166653707519858</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="Y3">
-        <v>-0.05704541825792401</v>
+        <v>-0.07476069202447427</v>
       </c>
       <c r="Z3">
-        <v>0.1207798383262007</v>
+        <v>0.1056554142919772</v>
       </c>
       <c r="AA3">
-        <v>0.05539705183071802</v>
+        <v>0.0124945199473915</v>
       </c>
       <c r="AB3">
-        <v>0.1166653707519858</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="AC3">
-        <v>-0.06126831892126775</v>
+        <v>-0.08345883262754149</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.032</v>
+        <v>-0.299</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,22 +809,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01265822784810127</v>
+        <v>-0.05319338196050525</v>
       </c>
       <c r="AK3">
-        <v>-0.007751937984496124</v>
+        <v>-0.0310455819748728</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.1155234657039711</v>
+        <v>-0.7973333333333333</v>
+      </c>
+      <c r="AQ3">
+        <v>-3.352941176470588</v>
       </c>
     </row>
     <row r="4">
@@ -850,10 +847,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.101</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="E4">
-        <v>-0.291</v>
+        <v>0.257</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -868,28 +865,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.014</v>
+        <v>0.093</v>
       </c>
       <c r="L4">
-        <v>0.2058823529411765</v>
+        <v>0.5961538461538461</v>
       </c>
       <c r="M4">
         <v>0.141</v>
       </c>
       <c r="N4">
-        <v>0.01775818639798488</v>
+        <v>0.02120300751879699</v>
       </c>
       <c r="O4">
-        <v>10.07142857142857</v>
+        <v>1.516129032258064</v>
       </c>
       <c r="P4">
         <v>0.141</v>
       </c>
       <c r="Q4">
-        <v>0.01775818639798488</v>
+        <v>0.02120300751879699</v>
       </c>
       <c r="R4">
-        <v>10.07142857142857</v>
+        <v>1.516129032258064</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,31 +895,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>0.1788413098236776</v>
+        <v>0.1518796992481203</v>
       </c>
       <c r="W4">
-        <v>0.004895104895104896</v>
+        <v>0.03217993079584775</v>
       </c>
       <c r="X4">
-        <v>0.1166653707519858</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="Y4">
-        <v>-0.1117702658568809</v>
+        <v>-0.06377342177908524</v>
       </c>
       <c r="Z4">
-        <v>0.05714285714285715</v>
+        <v>0.1054054054054054</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1166653707519858</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="AC4">
-        <v>-0.1166653707519858</v>
+        <v>-0.09595335257493298</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -934,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-1.42</v>
+        <v>-1.01</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -943,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.2177914110429447</v>
+        <v>-0.1790780141843971</v>
       </c>
       <c r="AK4">
-        <v>-0.9281045751633985</v>
+        <v>-0.3992094861660079</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -971,8 +968,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>-2</v>
+      </c>
+      <c r="J5">
+        <v>-2</v>
+      </c>
       <c r="K5">
-        <v>-0.052</v>
+        <v>-0.016</v>
+      </c>
+      <c r="L5">
+        <v>-2</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,25 +1014,25 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>-0.01200923787528868</v>
+        <v>-0.003773584905660377</v>
       </c>
       <c r="X5">
-        <v>0.1166653707519858</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="Y5">
-        <v>-0.1286746086272745</v>
+        <v>-0.09972693748059336</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.001886792452830189</v>
       </c>
       <c r="AA5">
-        <v>-0.01200923787528868</v>
+        <v>-0.003773584905660377</v>
       </c>
       <c r="AB5">
-        <v>0.1166653707519858</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="AC5">
-        <v>-0.1286746086272745</v>
+        <v>-0.09972693748059336</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1051,241 +1063,6 @@
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Jordanian for Developing and Financial Investment Company (ASE:JDFI)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K6">
-        <v>-0.031</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>-0.01435185185185185</v>
-      </c>
-      <c r="X6">
-        <v>0.1166653707519858</v>
-      </c>
-      <c r="Y6">
-        <v>-0.1310172226038376</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>-0.01435185185185185</v>
-      </c>
-      <c r="AB6">
-        <v>0.1166653707519858</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1310172226038376</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>-0</v>
-      </c>
-      <c r="AP6">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ammoun International Multilateral Investments Co. (ASE:AMON)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>1.548</v>
-      </c>
-      <c r="G7">
-        <v>-0.01207729468599034</v>
-      </c>
-      <c r="H7">
-        <v>-0.01207729468599034</v>
-      </c>
-      <c r="I7">
-        <v>-0.3357487922705314</v>
-      </c>
-      <c r="J7">
-        <v>-0.3357487922705314</v>
-      </c>
-      <c r="K7">
-        <v>-0.195</v>
-      </c>
-      <c r="L7">
-        <v>-0.2355072463768116</v>
-      </c>
-      <c r="M7">
-        <v>0.792</v>
-      </c>
-      <c r="N7">
-        <v>0.1166421207658321</v>
-      </c>
-      <c r="O7">
-        <v>-4.061538461538461</v>
-      </c>
-      <c r="P7">
-        <v>0.792</v>
-      </c>
-      <c r="Q7">
-        <v>0.1166421207658321</v>
-      </c>
-      <c r="R7">
-        <v>-4.061538461538461</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0.417</v>
-      </c>
-      <c r="V7">
-        <v>0.06141384388807069</v>
-      </c>
-      <c r="W7">
-        <v>-0.01772727272727273</v>
-      </c>
-      <c r="X7">
-        <v>0.1166653707519858</v>
-      </c>
-      <c r="Y7">
-        <v>-0.1343926434792585</v>
-      </c>
-      <c r="Z7">
-        <v>0.08335011073082343</v>
-      </c>
-      <c r="AA7">
-        <v>-0.02798469901348903</v>
-      </c>
-      <c r="AB7">
-        <v>0.1166653707519858</v>
-      </c>
-      <c r="AC7">
-        <v>-0.1446500697654748</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>-0.417</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.06543229248391652</v>
-      </c>
-      <c r="AK7">
-        <v>-0.04415969501217833</v>
-      </c>
-      <c r="AL7">
-        <v>0.003</v>
-      </c>
-      <c r="AM7">
-        <v>-0.055</v>
-      </c>
-      <c r="AN7">
-        <v>-0</v>
-      </c>
-      <c r="AO7">
-        <v>-92.66666666666667</v>
-      </c>
-      <c r="AP7">
-        <v>23.16666666666667</v>
-      </c>
-      <c r="AQ7">
-        <v>5.054545454545455</v>
       </c>
     </row>
   </sheetData>
